--- a/data/trans_dic/Q17F_D_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 23,28</t>
+          <t>5,4; 22,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 21,65</t>
+          <t>3,19; 20,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,99</t>
+          <t>3,28; 19,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 12,69</t>
+          <t>1,27; 12,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,67</t>
+          <t>4,38; 15,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 21,7</t>
+          <t>6,7; 20,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 37,01</t>
+          <t>7,56; 36,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,54</t>
+          <t>3,92; 13,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 15,02</t>
+          <t>5,0; 14,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,17</t>
+          <t>6,94; 16,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 24,21</t>
+          <t>4,85; 24,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 20,2</t>
+          <t>4,01; 19,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 15,24</t>
+          <t>3,23; 15,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 12,82</t>
+          <t>2,31; 12,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 20,15</t>
+          <t>2,14; 20,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 19,58</t>
+          <t>7,44; 19,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 17,45</t>
+          <t>6,97; 16,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 16,77</t>
+          <t>6,81; 16,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,83</t>
+          <t>1,84; 15,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 17,12</t>
+          <t>7,61; 16,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,68</t>
+          <t>6,7; 14,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,3</t>
+          <t>6,2; 13,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,68</t>
+          <t>2,81; 14,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 17,52</t>
+          <t>4,21; 16,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 18,14</t>
+          <t>6,49; 18,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 17,29</t>
+          <t>5,93; 17,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 25,72</t>
+          <t>7,73; 26,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 22,08</t>
+          <t>10,48; 22,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,01</t>
+          <t>7,06; 16,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 20,35</t>
+          <t>9,29; 20,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 26,76</t>
+          <t>13,84; 26,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 18,7</t>
+          <t>9,53; 18,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,89</t>
+          <t>7,75; 14,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 16,95</t>
+          <t>9,05; 16,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 24,06</t>
+          <t>13,54; 23,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 23,82</t>
+          <t>7,37; 23,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 23,77</t>
+          <t>8,37; 23,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,73</t>
+          <t>4,52; 13,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 29,25</t>
+          <t>14,84; 29,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,77</t>
+          <t>9,08; 21,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,31</t>
+          <t>6,89; 16,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 13,56</t>
+          <t>4,92; 13,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,78; 29,57</t>
+          <t>18,57; 29,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 19,43</t>
+          <t>9,64; 19,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,03</t>
+          <t>8,87; 16,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,03</t>
+          <t>5,47; 11,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 26,68</t>
+          <t>18,47; 27,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 21,39</t>
+          <t>8,39; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 20,39</t>
+          <t>7,94; 20,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 21,3</t>
+          <t>8,94; 22,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 33,28</t>
+          <t>18,9; 32,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 18,99</t>
+          <t>7,11; 18,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 16,29</t>
+          <t>6,28; 16,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 22,1</t>
+          <t>10,46; 22,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,14; 32,57</t>
+          <t>20,87; 32,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 17,09</t>
+          <t>9,0; 17,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 15,67</t>
+          <t>8,56; 16,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 19,82</t>
+          <t>11,04; 19,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,79; 30,85</t>
+          <t>21,26; 30,77</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,19; 24,13</t>
+          <t>10,91; 23,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,98; 27,52</t>
+          <t>12,58; 28,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 23,25</t>
+          <t>9,3; 22,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,69; 29,03</t>
+          <t>15,16; 28,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,28</t>
+          <t>3,52; 10,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 16,63</t>
+          <t>6,91; 16,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 17,91</t>
+          <t>7,92; 17,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 24,72</t>
+          <t>14,08; 24,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,23</t>
+          <t>8,07; 15,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,73</t>
+          <t>10,53; 19,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,91</t>
+          <t>9,84; 18,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,49</t>
+          <t>16,25; 24,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,72</t>
+          <t>2,65; 13,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,06</t>
+          <t>4,6; 15,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,76</t>
+          <t>6,11; 18,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 26,01</t>
+          <t>10,43; 25,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,46</t>
+          <t>2,83; 11,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,85</t>
+          <t>5,49; 14,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 19,71</t>
+          <t>7,54; 19,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,17</t>
+          <t>10,98; 21,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,76</t>
+          <t>3,45; 10,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,4</t>
+          <t>6,03; 13,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,15</t>
+          <t>8,56; 17,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 20,82</t>
+          <t>12,59; 20,83</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,89</t>
+          <t>9,76; 15,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,16</t>
+          <t>10,09; 15,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,39</t>
+          <t>8,56; 13,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,37</t>
+          <t>15,55; 21,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,79</t>
+          <t>8,64; 12,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,44</t>
+          <t>8,78; 12,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,69; 14,64</t>
+          <t>10,52; 14,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,3; 21,22</t>
+          <t>13,77; 21,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,96</t>
+          <t>9,77; 12,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,12</t>
+          <t>9,8; 12,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 13,43</t>
+          <t>10,43; 13,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,51; 20,45</t>
+          <t>15,62; 20,42</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2055; 11843</t>
+          <t>2747; 11371</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1019; 12563</t>
+          <t>1853; 12101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2075; 12169</t>
+          <t>2104; 12254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4636</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1103; 9325</t>
+          <t>930; 9053</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3876; 15892</t>
+          <t>4173; 14919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6879; 19848</t>
+          <t>6130; 18692</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3922; 19902</t>
+          <t>4066; 19885</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4842; 16842</t>
+          <t>4873; 16735</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7776; 23030</t>
+          <t>7673; 22293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10674; 26706</t>
+          <t>10798; 25914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3954; 20170</t>
+          <t>4041; 20746</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2883; 13831</t>
+          <t>2747; 13249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3123; 14544</t>
+          <t>3084; 14760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1939; 11059</t>
+          <t>1997; 10447</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1625; 15848</t>
+          <t>1680; 16488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10789; 28134</t>
+          <t>10690; 27496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10956; 27910</t>
+          <t>11142; 27171</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9569; 25026</t>
+          <t>10163; 25068</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2716; 25735</t>
+          <t>2999; 25858</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16137; 36324</t>
+          <t>16158; 36004</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17661; 37506</t>
+          <t>17120; 36729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13836; 31320</t>
+          <t>14608; 31830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6822; 33007</t>
+          <t>6769; 34813</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3850; 14493</t>
+          <t>3486; 13992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7740; 22243</t>
+          <t>7954; 22088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8831; 24427</t>
+          <t>8381; 25338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6067; 19536</t>
+          <t>5875; 19816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17168; 36842</t>
+          <t>17483; 37509</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12944; 30084</t>
+          <t>13258; 30915</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15500; 33472</t>
+          <t>15279; 32968</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15484; 29914</t>
+          <t>15472; 29866</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23813; 46679</t>
+          <t>23783; 45843</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24273; 46232</t>
+          <t>24063; 45541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27667; 51834</t>
+          <t>27661; 51582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24791; 45162</t>
+          <t>25423; 43750</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5828; 18493</t>
+          <t>5724; 18290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8882; 25548</t>
+          <t>8996; 25680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7122; 22088</t>
+          <t>7271; 22042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16694; 34481</t>
+          <t>17498; 35268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11570; 28022</t>
+          <t>12253; 29290</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14545; 32597</t>
+          <t>12967; 31886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8485; 23307</t>
+          <t>8464; 23818</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30236; 47604</t>
+          <t>29897; 47388</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20461; 41303</t>
+          <t>20493; 42290</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26477; 50389</t>
+          <t>26240; 49908</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17952; 40019</t>
+          <t>18199; 38580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51730; 74417</t>
+          <t>51498; 75969</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10094; 24939</t>
+          <t>9780; 24984</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9995; 25930</t>
+          <t>10099; 25699</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12528; 29565</t>
+          <t>12407; 31134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24647; 43093</t>
+          <t>24474; 42668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10043; 27037</t>
+          <t>10118; 25914</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9276; 24497</t>
+          <t>9446; 24431</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19228; 41097</t>
+          <t>19455; 41575</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27320; 42093</t>
+          <t>26976; 41850</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23569; 44271</t>
+          <t>23300; 45409</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21895; 43492</t>
+          <t>23767; 44920</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36553; 64375</t>
+          <t>35859; 63884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56377; 79814</t>
+          <t>55004; 79614</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14178; 30571</t>
+          <t>13822; 29563</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15229; 34972</t>
+          <t>15990; 36263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10953; 28056</t>
+          <t>11220; 27068</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15845; 29327</t>
+          <t>15314; 29204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5358; 16928</t>
+          <t>5288; 16355</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9872; 24247</t>
+          <t>10067; 24427</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14445; 31786</t>
+          <t>14052; 31924</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15707; 27809</t>
+          <t>15846; 27375</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22345; 42149</t>
+          <t>22324; 41903</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29572; 53837</t>
+          <t>28745; 54458</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29746; 53397</t>
+          <t>29331; 54060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34816; 52301</t>
+          <t>34699; 52117</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1967; 11253</t>
+          <t>2172; 10815</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4918; 18437</t>
+          <t>4975; 17100</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6823; 19565</t>
+          <t>6370; 19027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8200; 19202</t>
+          <t>7701; 18722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4459; 17974</t>
+          <t>4431; 17853</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9959; 26800</t>
+          <t>9909; 26488</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12834; 32841</t>
+          <t>12557; 31972</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13539; 25510</t>
+          <t>13239; 25862</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8799; 25705</t>
+          <t>8250; 24702</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17899; 38666</t>
+          <t>17412; 37557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22219; 46446</t>
+          <t>23182; 47192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24263; 40462</t>
+          <t>24470; 40486</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>59288; 90084</t>
+          <t>59039; 90940</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>75938; 113125</t>
+          <t>75237; 113769</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71659; 109319</t>
+          <t>69880; 108106</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>92863; 129600</t>
+          <t>94283; 131578</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85481; 123824</t>
+          <t>83660; 124655</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95519; 137801</t>
+          <t>97245; 138518</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>118387; 162123</t>
+          <t>116471; 161563</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>121737; 180635</t>
+          <t>117282; 181987</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153636; 203874</t>
+          <t>153644; 203563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>184530; 243251</t>
+          <t>181779; 238738</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>196733; 258302</t>
+          <t>200623; 260124</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>226106; 298147</t>
+          <t>227705; 297678</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q17F_D_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 22,35</t>
+          <t>4,21; 22,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 20,85</t>
+          <t>3,19; 20,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 19,12</t>
+          <t>3,24; 19,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,32</t>
+          <t>1,49; 12,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 15,65</t>
+          <t>4,09; 15,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 20,44</t>
+          <t>7,41; 20,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 36,98</t>
+          <t>6,27; 32,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 13,46</t>
+          <t>3,86; 13,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 14,53</t>
+          <t>4,46; 14,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 16,66</t>
+          <t>6,45; 17,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 24,9</t>
+          <t>5,0; 24,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 19,34</t>
+          <t>3,75; 20,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 15,46</t>
+          <t>3,99; 14,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,11</t>
+          <t>2,25; 12,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,97</t>
+          <t>2,8; 22,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 19,13</t>
+          <t>7,7; 20,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 16,99</t>
+          <t>6,89; 16,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 16,8</t>
+          <t>6,93; 16,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,9</t>
+          <t>8,2; 23,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,97</t>
+          <t>7,55; 16,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,38</t>
+          <t>6,89; 14,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,52</t>
+          <t>6,05; 13,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,43</t>
+          <t>7,4; 18,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,91</t>
+          <t>4,48; 16,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 18,01</t>
+          <t>6,11; 17,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 17,94</t>
+          <t>6,15; 17,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 26,09</t>
+          <t>6,92; 24,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 22,48</t>
+          <t>11,06; 22,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 16,46</t>
+          <t>7,05; 16,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 20,04</t>
+          <t>8,8; 20,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 26,72</t>
+          <t>14,04; 26,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 18,37</t>
+          <t>9,63; 18,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,67</t>
+          <t>7,61; 14,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 16,87</t>
+          <t>8,68; 16,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 23,31</t>
+          <t>12,78; 22,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 23,55</t>
+          <t>7,78; 23,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 23,89</t>
+          <t>8,4; 23,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 13,7</t>
+          <t>4,05; 13,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 29,91</t>
+          <t>14,56; 29,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,7</t>
+          <t>8,78; 21,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,93</t>
+          <t>7,46; 16,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 13,85</t>
+          <t>4,85; 14,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,57; 29,44</t>
+          <t>20,34; 31,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 19,89</t>
+          <t>9,98; 20,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,87</t>
+          <t>9,0; 17,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,59</t>
+          <t>5,23; 12,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 27,24</t>
+          <t>19,55; 28,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 21,43</t>
+          <t>8,74; 21,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 20,21</t>
+          <t>8,01; 19,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 22,43</t>
+          <t>9,19; 22,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,9; 32,96</t>
+          <t>19,35; 34,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 18,2</t>
+          <t>7,2; 17,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 16,25</t>
+          <t>6,19; 16,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 22,35</t>
+          <t>10,37; 22,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,87; 32,38</t>
+          <t>22,27; 33,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,53</t>
+          <t>9,12; 17,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 16,19</t>
+          <t>8,08; 15,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 19,67</t>
+          <t>11,32; 20,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,26; 30,77</t>
+          <t>22,2; 31,5</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,91; 23,33</t>
+          <t>11,17; 24,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 28,53</t>
+          <t>12,5; 28,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,3; 22,43</t>
+          <t>8,82; 21,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,16; 28,91</t>
+          <t>15,53; 29,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,9</t>
+          <t>3,64; 11,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,76</t>
+          <t>6,45; 16,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 17,99</t>
+          <t>8,28; 18,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,33</t>
+          <t>14,41; 25,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,14</t>
+          <t>8,09; 15,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,53; 19,96</t>
+          <t>10,52; 19,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,13</t>
+          <t>9,79; 17,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,41</t>
+          <t>16,52; 24,93</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,18</t>
+          <t>3,02; 13,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,82</t>
+          <t>4,61; 16,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 18,25</t>
+          <t>6,31; 18,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,43; 25,36</t>
+          <t>11,76; 26,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 11,38</t>
+          <t>2,92; 12,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,67</t>
+          <t>6,05; 15,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 19,19</t>
+          <t>7,59; 19,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 21,46</t>
+          <t>11,25; 21,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,34</t>
+          <t>3,55; 10,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,01</t>
+          <t>6,32; 13,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 17,42</t>
+          <t>8,48; 17,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,59; 20,83</t>
+          <t>12,76; 21,38</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,03</t>
+          <t>9,69; 15,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,25</t>
+          <t>10,15; 15,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,24</t>
+          <t>8,61; 13,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,55; 21,7</t>
+          <t>15,78; 21,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,87</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,5</t>
+          <t>8,94; 12,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,59</t>
+          <t>10,61; 14,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,37</t>
+          <t>18,33; 22,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,77; 12,94</t>
+          <t>9,88; 13,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,88</t>
+          <t>9,92; 12,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,52</t>
+          <t>10,31; 13,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,42</t>
+          <t>17,89; 21,58</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10432</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2747; 11371</t>
+          <t>2140; 11677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1853; 12101</t>
+          <t>1853; 11659</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2104; 12254</t>
+          <t>2078; 12190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>930; 9053</t>
+          <t>1093; 9305</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4173; 14919</t>
+          <t>3902; 14665</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6130; 18692</t>
+          <t>6773; 18941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4066; 19885</t>
+          <t>4003; 20540</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4873; 16735</t>
+          <t>4803; 16684</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7673; 22293</t>
+          <t>6847; 21911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10798; 25914</t>
+          <t>10033; 26583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4041; 20746</t>
+          <t>4509; 22331</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>22379</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2747; 13249</t>
+          <t>2571; 13950</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3084; 14760</t>
+          <t>3813; 13912</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1997; 10447</t>
+          <t>1939; 10479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1680; 16488</t>
+          <t>2292; 18591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10690; 27496</t>
+          <t>11071; 28743</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11142; 27171</t>
+          <t>11026; 26893</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10163; 25068</t>
+          <t>10335; 24855</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2999; 25858</t>
+          <t>8621; 24539</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16158; 36004</t>
+          <t>16018; 35931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17120; 36729</t>
+          <t>17589; 36565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14608; 31830</t>
+          <t>14247; 32175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6769; 34813</t>
+          <t>13823; 34502</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33403</t>
+          <t>36668</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3486; 13992</t>
+          <t>3704; 13721</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7954; 22088</t>
+          <t>7492; 21262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8381; 25338</t>
+          <t>8686; 24768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5875; 19816</t>
+          <t>6027; 21245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17483; 37509</t>
+          <t>18453; 37628</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13258; 30915</t>
+          <t>13241; 31071</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15279; 32968</t>
+          <t>14482; 33298</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15472; 29866</t>
+          <t>17837; 33777</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23783; 45843</t>
+          <t>24045; 45204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24063; 45541</t>
+          <t>23635; 45995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27661; 51582</t>
+          <t>26528; 51744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25423; 43750</t>
+          <t>27365; 48468</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24568</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62870</t>
+          <t>71905</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5724; 18290</t>
+          <t>6045; 18521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8996; 25680</t>
+          <t>9026; 24779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7271; 22042</t>
+          <t>6522; 22491</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17498; 35268</t>
+          <t>19116; 38723</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12253; 29290</t>
+          <t>11847; 28488</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12967; 31886</t>
+          <t>14057; 31843</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8464; 23818</t>
+          <t>8338; 24167</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29897; 47388</t>
+          <t>34994; 53785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20493; 42290</t>
+          <t>21225; 43127</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26240; 49908</t>
+          <t>26636; 50288</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18199; 38580</t>
+          <t>17420; 39971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51498; 75969</t>
+          <t>59292; 86727</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>34516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>74372</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9780; 24984</t>
+          <t>10193; 25121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10099; 25699</t>
+          <t>10192; 24795</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12407; 31134</t>
+          <t>12750; 31285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24474; 42668</t>
+          <t>25565; 45013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10118; 25914</t>
+          <t>10248; 25257</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9446; 24431</t>
+          <t>9312; 25255</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19455; 41575</t>
+          <t>19291; 41191</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26976; 41850</t>
+          <t>32501; 49074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23300; 45409</t>
+          <t>23632; 44686</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23767; 44920</t>
+          <t>22425; 43987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35859; 63884</t>
+          <t>36777; 66541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55004; 79614</t>
+          <t>61726; 87587</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>47583</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13822; 29563</t>
+          <t>14149; 30790</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15990; 36263</t>
+          <t>15891; 35790</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11220; 27068</t>
+          <t>10640; 26488</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15314; 29204</t>
+          <t>17252; 32613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5288; 16355</t>
+          <t>5467; 16682</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10067; 24427</t>
+          <t>9400; 24247</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14052; 31924</t>
+          <t>14690; 32439</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15846; 27375</t>
+          <t>17946; 31395</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22324; 41903</t>
+          <t>22383; 43381</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28745; 54458</t>
+          <t>28710; 53178</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29331; 54060</t>
+          <t>29197; 52345</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34699; 52117</t>
+          <t>38925; 58751</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>35908</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2172; 10815</t>
+          <t>2477; 11054</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4975; 17100</t>
+          <t>4985; 18061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6370; 19027</t>
+          <t>6576; 19310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7701; 18722</t>
+          <t>9631; 21665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4431; 17853</t>
+          <t>4574; 19181</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9909; 26488</t>
+          <t>10928; 27306</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12557; 31972</t>
+          <t>12642; 32969</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13239; 25862</t>
+          <t>15187; 29074</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8250; 24702</t>
+          <t>8480; 24207</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17412; 37557</t>
+          <t>18230; 38290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23182; 47192</t>
+          <t>22965; 46699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24470; 40486</t>
+          <t>27692; 46379</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>120965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>299248</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>59039; 90940</t>
+          <t>58656; 91638</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>75237; 113769</t>
+          <t>75691; 113651</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>69880; 108106</t>
+          <t>70285; 107819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>94283; 131578</t>
+          <t>102826; 142922</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>83660; 124655</t>
+          <t>84711; 124464</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97245; 138518</t>
+          <t>99034; 139149</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>116471; 161563</t>
+          <t>117428; 164343</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>117282; 181987</t>
+          <t>160135; 200627</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153644; 203563</t>
+          <t>155508; 205889</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>181779; 238738</t>
+          <t>183941; 239724</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>200623; 260124</t>
+          <t>198395; 257585</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>227705; 297678</t>
+          <t>272816; 329167</t>
         </is>
       </c>
     </row>
